--- a/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
+++ b/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rod\Desktop\EPS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\bldgs\BPSfDSPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{0C71C972-6EB7-4463-8E00-9561AF9B13FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F010D94-C047-49CA-944F-5BA970BEE308}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0869BFB6-8993-46D4-92F4-176DDAC562A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32115" yWindow="1530" windowWidth="23310" windowHeight="13380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="7" r:id="rId1"/>
-    <sheet name="BPSfDSPV" sheetId="8" r:id="rId2"/>
+    <sheet name="BPSfDSPC" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -79,7 +79,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,18 +432,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="61.5703125" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -451,10 +451,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -471,13 +471,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -632,7 +632,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1097,13 +1097,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
     </row>
   </sheetData>
@@ -1113,6 +1113,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -1256,12 +1262,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1272,13 +1272,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C41D4B-45D5-42A0-99A4-938B3ACB2BC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BCB5BCB-0E87-47FD-AF4C-8354FAD51360}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BCB5BCB-0E87-47FD-AF4C-8354FAD51360}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C41D4B-45D5-42A0-99A4-938B3ACB2BC7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9661B59D-86F4-4600-BE69-F47BDA585B84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9661B59D-86F4-4600-BE69-F47BDA585B84}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
+++ b/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\bldgs\BPSfDSPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\bldgs\BPSfDSPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0869BFB6-8993-46D4-92F4-176DDAC562A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9891901F-0CE6-460E-9995-1FADB76A4981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32115" yWindow="1530" windowWidth="23310" windowHeight="13380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="7" r:id="rId1"/>
@@ -116,17 +116,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,641 +469,633 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.85546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="4" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="4">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="4">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="D1" s="4">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="4">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="4">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="4">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="H1" s="4">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="4">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="J1" s="4">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="K1" s="4">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="L1" s="4">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="M1" s="4">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="N1" s="4">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="O1" s="4">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="P1" s="4">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="Q1" s="4">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="R1" s="4">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="S1" s="4">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="T1" s="4">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="U1" s="4">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="V1" s="4">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="W1" s="4">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="X1" s="4">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Y1" s="4">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="Z1" s="4">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AA1" s="4">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AB1" s="4">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AC1" s="4">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AD1" s="4">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AE1" s="4">
         <v>2050</v>
       </c>
-      <c r="AF1">
+      <c r="AF1" s="4">
         <v>2051</v>
       </c>
-      <c r="AG1">
+      <c r="AG1" s="4">
         <v>2052</v>
       </c>
-      <c r="AH1">
+      <c r="AH1" s="4">
         <v>2053</v>
       </c>
-      <c r="AI1">
+      <c r="AI1" s="4">
         <v>2054</v>
       </c>
-      <c r="AJ1">
+      <c r="AJ1" s="4">
         <v>2055</v>
       </c>
-      <c r="AK1">
+      <c r="AK1" s="4">
         <v>2056</v>
       </c>
-      <c r="AL1">
+      <c r="AL1" s="4">
         <v>2057</v>
       </c>
-      <c r="AM1">
+      <c r="AM1" s="4">
         <v>2058</v>
       </c>
-      <c r="AN1">
+      <c r="AN1" s="4">
         <v>2059</v>
       </c>
-      <c r="AO1">
+      <c r="AO1" s="4">
         <v>2060</v>
       </c>
-      <c r="AP1">
+      <c r="AP1" s="4">
         <v>2061</v>
       </c>
-      <c r="AQ1">
+      <c r="AQ1" s="4">
         <v>2062</v>
       </c>
-      <c r="AR1">
+      <c r="AR1" s="4">
         <v>2063</v>
       </c>
-      <c r="AS1">
+      <c r="AS1" s="4">
         <v>2064</v>
       </c>
-      <c r="AT1">
+      <c r="AT1" s="4">
         <v>2065</v>
       </c>
-      <c r="AU1">
+      <c r="AU1" s="4">
         <v>2066</v>
       </c>
-      <c r="AV1">
+      <c r="AV1" s="4">
         <v>2067</v>
       </c>
-      <c r="AW1">
+      <c r="AW1" s="4">
         <v>2068</v>
       </c>
-      <c r="AX1">
+      <c r="AX1" s="4">
         <v>2069</v>
       </c>
-      <c r="AY1">
+      <c r="AY1" s="4">
         <v>2070</v>
       </c>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5">
-        <v>0</v>
-      </c>
-      <c r="L2" s="5">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5">
-        <v>0</v>
-      </c>
-      <c r="W2" s="5">
-        <v>0</v>
-      </c>
-      <c r="X2" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY2" s="5">
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>0</v>
-      </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" s="5">
-        <v>0</v>
-      </c>
-      <c r="T3" s="5">
-        <v>0</v>
-      </c>
-      <c r="U3" s="5">
-        <v>0</v>
-      </c>
-      <c r="V3" s="5">
-        <v>0</v>
-      </c>
-      <c r="W3" s="5">
-        <v>0</v>
-      </c>
-      <c r="X3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY3" s="5">
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="5">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>0</v>
-      </c>
-      <c r="R4" s="5">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5">
-        <v>0</v>
-      </c>
-      <c r="T4" s="5">
-        <v>0</v>
-      </c>
-      <c r="U4" s="5">
-        <v>0</v>
-      </c>
-      <c r="V4" s="5">
-        <v>0</v>
-      </c>
-      <c r="W4" s="5">
-        <v>0</v>
-      </c>
-      <c r="X4" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4">
+        <v>0</v>
+      </c>
+      <c r="U4" s="4">
+        <v>0</v>
+      </c>
+      <c r="V4" s="4">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1113,9 +1104,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1263,19 +1257,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BCB5BCB-0E87-47FD-AF4C-8354FAD51360}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9661B59D-86F4-4600-BE69-F47BDA585B84}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1299,9 +1289,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9661B59D-86F4-4600-BE69-F47BDA585B84}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BCB5BCB-0E87-47FD-AF4C-8354FAD51360}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>